--- a/Apperater.xlsx
+++ b/Apperater.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stuja\OneDrive\Dokumenter\Studie\0. Etterstudium\Eninf Oblig 1\git2\in5410_intelligent_load_scheduling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877DB33F-98D4-4D76-A591-07231DE4B6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC1D77C-3270-4615-87E5-54C912DB410A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -51,19 +62,19 @@
     <t>Vaskemaskin</t>
   </si>
   <si>
-    <t>2.0</t>
-  </si>
-  <si>
     <t>Elbillader</t>
   </si>
   <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>Varmekabler</t>
-  </si>
-  <si>
-    <t>3.0</t>
+    <t>1.44</t>
+  </si>
+  <si>
+    <t>1.94</t>
+  </si>
+  <si>
+    <t>9.9</t>
+  </si>
+  <si>
+    <t>Oppvaskmaskin</t>
   </si>
 </sst>
 </file>
@@ -127,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -141,6 +152,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="34.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -447,21 +463,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="C2" s="3">
         <v>2</v>
       </c>
       <c r="D2" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F2" s="3">
         <v>0</v>
@@ -470,21 +486,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
@@ -493,21 +509,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C4" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E4" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F4" s="3">
         <v>1</v>
@@ -515,6 +531,12 @@
       <c r="G4" s="4">
         <v>0</v>
       </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C7" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
